--- a/results/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/results/att_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.043</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.061</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -672,7 +672,7 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.008999999999999999</v>
@@ -699,10 +699,10 @@
         <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1131,10 +1131,10 @@
         <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,13 +1388,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>554.8407173044708</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07201647252918561</v>
+        <v>0.07201588164977409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2496220969064754</v>
+        <v>0.2496221955703657</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.444430102069432</v>
+        <v>1.415563718989384</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3600009645893537</v>
+        <v>0.3653792945421989</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7388411770746193</v>
+        <v>0.6994334609900217</v>
       </c>
       <c r="E2" t="n">
-        <v>2.150019027064245</v>
+        <v>2.131693976988746</v>
       </c>
       <c r="F2" t="n">
-        <v>6.013126820637343e-05</v>
+        <v>0.0001069620034728388</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01589747344353674</v>
+        <v>0.01406648442462931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07027074399724166</v>
+        <v>0.06948450970190397</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1218306539578911</v>
+        <v>-0.1221206520745264</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1536256008449646</v>
+        <v>0.150253620923785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.821021177128507</v>
+        <v>0.8395723070577608</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2082966979437955</v>
+        <v>0.1934376197861498</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1550014950042996</v>
+        <v>0.1561342593458453</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09550064981449682</v>
+        <v>-0.1125799052845435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5120940457020878</v>
+        <v>0.4994551448568431</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1790011981136211</v>
+        <v>0.2153756879251698</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07314184234528501</v>
+        <v>0.08228016691387019</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1193527467109534</v>
+        <v>0.1200746414081912</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.160785242664115</v>
+        <v>-0.1530618057027465</v>
       </c>
       <c r="E5" t="n">
-        <v>0.307068927354685</v>
+        <v>0.3176221395304868</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5399948547085109</v>
+        <v>0.4931913324621549</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2640920575032634</v>
+        <v>0.2682770111457031</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1308213627417742</v>
+        <v>0.1300132400848991</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007686898120935926</v>
+        <v>0.01345574306594161</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5204972168855909</v>
+        <v>0.5230982792254646</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04351604696337923</v>
+        <v>0.03906902418388693</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04705714408797273</v>
+        <v>0.05866897476674996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1397869309910783</v>
+        <v>0.1386554783743341</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2269202061639266</v>
+        <v>-0.2130907691061173</v>
       </c>
       <c r="E7" t="n">
-        <v>0.321034494339872</v>
+        <v>0.3304287186396172</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7363922271311671</v>
+        <v>0.6722020875369374</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06309400148132728</v>
+        <v>0.06280541537249594</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1473152067365991</v>
+        <v>0.1473120129983402</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2256384980974793</v>
+        <v>-0.2259208245943471</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3518265010601339</v>
+        <v>0.351531655339339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6684381623202673</v>
+        <v>0.6698580785094381</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1288291764782645</v>
+        <v>0.1390231384900846</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1237603403433366</v>
+        <v>0.1202882283264922</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1137366333090947</v>
+        <v>-0.09673745679397092</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3713949862656238</v>
+        <v>0.3747837337741401</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2978955659191387</v>
+        <v>0.2477833667498968</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04425185344559728</v>
+        <v>0.02793986317350431</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1961161836213611</v>
+        <v>0.1999310656891027</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3401288032377144</v>
+        <v>-0.3639178249678487</v>
       </c>
       <c r="E10" t="n">
-        <v>0.428632510128909</v>
+        <v>0.4197975513148574</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8214806431320605</v>
+        <v>0.888859508592426</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.04965393761379477</v>
+        <v>-0.07356614672567942</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2061905983271696</v>
+        <v>0.2061356399317549</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4537800842858118</v>
+        <v>-0.4775845769220356</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3544722090582223</v>
+        <v>0.3304522834706768</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8096979444921302</v>
+        <v>0.7211799737560189</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05229176639268616</v>
+        <v>0.03199774539716495</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2005769088916779</v>
+        <v>0.2061594449032444</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3408317511653742</v>
+        <v>-0.3720673416859638</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4454152839507465</v>
+        <v>0.4360628324802936</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7943186127966479</v>
+        <v>0.8766567670029287</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02116957991689462</v>
+        <v>-0.006374277414136538</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1984534783476406</v>
+        <v>0.1965463686430554</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3677920902511805</v>
+        <v>-0.3915980812466577</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4101312500849697</v>
+        <v>0.3788495264183846</v>
       </c>
       <c r="F13" t="n">
-        <v>0.915048595043758</v>
+        <v>0.9741280078152982</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2104631569266432</v>
+        <v>-0.2378369521738854</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2075111756019344</v>
+        <v>0.2077401681853182</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6171775874960014</v>
+        <v>-0.6450001999594027</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1962512736427149</v>
+        <v>0.1693262956116319</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3104750920137385</v>
+        <v>0.2522600895661907</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.06996298231267936</v>
+        <v>-0.08511172439276492</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2172181239900265</v>
+        <v>0.2148668528732524</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4957026821224872</v>
+        <v>-0.5062430174958062</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3557767174971286</v>
+        <v>0.3360195687102764</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7473873151233605</v>
+        <v>0.6920210823807</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1228455868899026</v>
+        <v>0.09645326976338144</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1989887997999011</v>
+        <v>0.1999648883531904</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2671652940447548</v>
+        <v>-0.2954707095814447</v>
       </c>
       <c r="E16" t="n">
-        <v>0.51285646782456</v>
+        <v>0.4883772491082075</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5370043866019107</v>
+        <v>0.6295566025541435</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2274144806342348</v>
+        <v>-0.265896000151903</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1973096286939363</v>
+        <v>0.1973633420962457</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6141342466773209</v>
+        <v>-0.6527210425290024</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1593052854088513</v>
+        <v>0.1209290422251965</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2490841714850129</v>
+        <v>0.1779026046618583</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1429222550504737</v>
+        <v>0.1410581106617723</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1841372943948849</v>
+        <v>0.186298220165677</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2179802101741499</v>
+        <v>-0.2240796912468683</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5038247202750974</v>
+        <v>0.506195912570413</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4376472983448069</v>
+        <v>0.448952241814446</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.06357677136230566</v>
+        <v>-0.08344985283767321</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2103369006978352</v>
+        <v>0.204135490748071</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4758295213498405</v>
+        <v>-0.4835480626703018</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3486759786252291</v>
+        <v>0.3166483569949554</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7624526371502093</v>
+        <v>0.6826890852425092</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2432356097571376</v>
+        <v>-0.2678101521998023</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1917527074581269</v>
+        <v>0.1911082668602472</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6190640103131113</v>
+        <v>-0.6423754723937563</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1325927907988361</v>
+        <v>0.1067551679941518</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2046244753099549</v>
+        <v>0.1611085253078239</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2157625447106657</v>
+        <v>-0.2357850011436259</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1834682680814145</v>
+        <v>0.1852596407770953</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5753537424561778</v>
+        <v>-0.5988872248555608</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1438286530348463</v>
+        <v>0.127317222568309</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2395864657019914</v>
+        <v>0.2031148290793011</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08719584054218103</v>
+        <v>0.05887556586940938</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2015561612912558</v>
+        <v>0.19647958528987</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3078469764508265</v>
+        <v>-0.3262173449961016</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4822386575351886</v>
+        <v>0.4439684767349204</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6652958536188865</v>
+        <v>0.764442362331275</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1063727343733667</v>
+        <v>-0.1370978385961138</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2065486338202119</v>
+        <v>0.2015940271276354</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5112006177169337</v>
+        <v>-0.5322148712646697</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2984551489702003</v>
+        <v>0.2580191940724421</v>
       </c>
       <c r="F23" t="n">
-        <v>0.606552384115953</v>
+        <v>0.496460803011269</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1265757161712208</v>
+        <v>0.1314300700432246</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1012405670202358</v>
+        <v>0.1025093436987394</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.07185214896285497</v>
+        <v>-0.0694845516851425</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3250035813052965</v>
+        <v>0.3323446917715917</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2112093290939866</v>
+        <v>0.1997978500285618</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.02123594415741662</v>
+        <v>0.03463267714177365</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08684556749948509</v>
+        <v>0.08275182901981312</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1489782403585164</v>
+        <v>-0.1275579273918765</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1914501286733496</v>
+        <v>0.1968232816754238</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8068239590773969</v>
+        <v>0.6755724289525703</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1417934129670144</v>
+        <v>-0.1488260434975336</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1054997521258914</v>
+        <v>0.1041192044224463</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3485691275116646</v>
+        <v>-0.352895934264492</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06498230157763574</v>
+        <v>0.0552438472694248</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1789430349230666</v>
+        <v>0.1528946709271377</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.02591960064562005</v>
+        <v>-0.03169527812066093</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1131002021957283</v>
+        <v>0.1100545842581245</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2475919235934455</v>
+        <v>-0.2473982996001137</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1957527223022054</v>
+        <v>0.1840077433587918</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8187338522694707</v>
+        <v>0.7733498139601129</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1486822423187994</v>
+        <v>0.1415579970155403</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1177405696763044</v>
+        <v>0.1155062953631746</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.08208503376598614</v>
+        <v>-0.08483018188392771</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3794495184035849</v>
+        <v>0.3679461759150082</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2066627410803731</v>
+        <v>0.2203704862681721</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0231099767686504</v>
+        <v>-0.02793447775400487</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1085962316803818</v>
+        <v>0.1096742534746419</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2359546797189665</v>
+        <v>-0.2428920645956199</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1897347261816657</v>
+        <v>0.1870231090876101</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8314779453809236</v>
+        <v>0.7989516794020012</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2591768318423447</v>
+        <v>0.2582177129441012</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03580784780244857</v>
+        <v>0.03790343166340342</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1889947397856538</v>
+        <v>0.1839283519933554</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3293589238990356</v>
+        <v>0.332507073894847</v>
       </c>
       <c r="F30" t="n">
-        <v>4.553841777150192e-13</v>
+        <v>9.590676754514887e-12</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4739173243059975</v>
+        <v>-0.0139827428308932</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03471764090288941</v>
+        <v>0.01558971665227979</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4058719985081396</v>
+        <v>-0.04453802599854594</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5419626501038554</v>
+        <v>0.01657254033675953</v>
       </c>
       <c r="F31" t="n">
-        <v>2.001681582912061e-42</v>
+        <v>0.3697611220226279</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.007197916805801252</v>
+        <v>0.001915888013808374</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005210070542571189</v>
+        <v>0.004864009007753433</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01740946742615384</v>
+        <v>-0.00761739446186676</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003013633814551337</v>
+        <v>0.01144917048948351</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1671132267059805</v>
+        <v>0.6936617214919623</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003623927746821954</v>
+        <v>0.4698373208221376</v>
       </c>
       <c r="C33" t="n">
-        <v>0.005008872242520746</v>
+        <v>0.03332861578287753</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.006193281451681083</v>
+        <v>0.4045144342331244</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01344113694532499</v>
+        <v>0.5351602074111508</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4693716899003004</v>
+        <v>3.956166429178575e-45</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0007496268654860604</v>
+        <v>0.001079790152347923</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006042174213307456</v>
+        <v>0.005978338076640254</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.01109281698091319</v>
+        <v>-0.01063753716527143</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01259207071188531</v>
+        <v>0.01279711746996728</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9012632174386752</v>
+        <v>0.8566681240955272</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.06419718472678054</v>
+        <v>0.004135564358761949</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07567111108912947</v>
+        <v>0.004941189696127541</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0841154676780427</v>
+        <v>-0.005548989486428446</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2125098371316038</v>
+        <v>0.01382011820395234</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3962313250751351</v>
+        <v>0.402616618830529</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001602646801936641</v>
+        <v>0.06813476221211855</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01568575841010545</v>
+        <v>0.0748965559215783</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0291408747520663</v>
+        <v>-0.07865978996026506</v>
       </c>
       <c r="E36" t="n">
-        <v>0.03234616835593958</v>
+        <v>0.2149293143845021</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9186200766052697</v>
+        <v>0.3629711281145495</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.350970771285248</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4605522587714034</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>3.313590542287848e-07</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02128055977478192</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09751395156308111</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.827249191641336</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2245966634275915</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329354389845562</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3349449904957182</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8167052829997485</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1617156577703267</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>4.412210487480358e-07</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03599538577094948</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1898688322218615</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8496380437366924</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2765708211818085</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1824472225347018</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129545920374235</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102648615599912</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1853641405651108</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519401263365121</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745743640527194</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1615402513662274</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.164188141358052e-08</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04349724922704642</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655215602978132</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8698743077153893</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2685655156863916</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761865361461748</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3308484806726052</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08406558527820192</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251020166800007</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7377037334343584</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04159103469582721</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.255561465250315</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707201879025983</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05097157642059893</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2615504699624188</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8454850334004391</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1235593461635321</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2569613848518211</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6306245929938302</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002490750131026257</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2457746491930773</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9919141495524532</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1110262478895003</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594324060220158</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6686814903924607</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1338440250599403</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2694490717592011</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6193779257550096</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02068301206114321</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2629683391871477</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9373093461992266</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0686991433762508</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617458461247386</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7929629071620667</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2112158738988716</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2400889859196068</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3790001987958982</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.159933319308369</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2649283257747139</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5460529306471213</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4920005620651325</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2884409459397611</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08805953197431808</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9425285809878476</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1559773650465781</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>1.515312581506736e-09</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5768512495314141</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1130405709043027</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>3.342294640071132e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2384858887162336</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1457315480836286</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1017404238903948</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04585234373593617</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1593109532353293</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7734870970055308</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07857740431296747</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1565335672967476</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6156785148897228</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09755305493394664</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1499487653516257</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5153202832397639</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006860378637723895</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006945236405256705</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3232594861617505</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002646425713821547</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007095424075339026</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7091660102282209</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
@@ -2855,45 +2855,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004895000819746557</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008684655396149939</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5730005966817302</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2261835420647834</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1139281184793711</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04710910483736543</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01540023496026497</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0213723694247541</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.47117565131408</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>
